--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_DK.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_DK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cloude cowork\スキル秘伝HP\skill-sigil-web\資料\説明(パッシブ・スキル)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71155DE5-5C85-4BD9-9178-EA31358961EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5774260D-3268-4095-852D-763A2458E9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="パッシブ(①)" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,14 @@
     <sheet name="ラバムスキル(3)" sheetId="19" r:id="rId19"/>
     <sheet name="ラバムスキル(4)" sheetId="20" r:id="rId20"/>
     <sheet name="スキル(黒精霊の怒り)" sheetId="21" r:id="rId21"/>
+    <sheet name="プロフィール" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="393">
   <si>
     <t>韓国語</t>
   </si>
@@ -78,6 +79,9 @@
     <t>太刀を操り、闇の魔術と洗練された剣術で敵を容赦なく切り倒す。</t>
   </si>
   <si>
+    <t>太刀を振るい、闇の魔法と巧みな剣術で敵を容赦なく斬り伏せる。</t>
+  </si>
+  <si>
     <t>・피격 시 3초 간 모험가에게 받는 피해량 감소 50%</t>
   </si>
   <si>
@@ -87,6 +91,9 @@
     <t>・命中時、3秒間冒険者から受けるダメージ-50%</t>
   </si>
   <si>
+    <t>・攻撃された時、3秒間冒険者から受けるダメージ量50%減少</t>
+  </si>
+  <si>
     <t>　・(재사용 대기 시간 15초 )</t>
   </si>
   <si>
@@ -96,6 +103,9 @@
     <t>　・(再使用待機時間: 15秒)</t>
   </si>
   <si>
+    <t>（再使用待機時間15秒）</t>
+  </si>
+  <si>
     <t>・기술 사용 시 마력 12 회복</t>
   </si>
   <si>
@@ -105,6 +115,9 @@
     <t>・技術使用時に魔力を12回復</t>
   </si>
   <si>
+    <t>・スキル使用時、魔力12回復</t>
+  </si>
+  <si>
     <t>・기술 사용 시 마력 40 을 소모하여 해당 기술의 피해량이 20% 증가</t>
   </si>
   <si>
@@ -114,6 +127,9 @@
     <t>・技術使用時に40魔力を消費し、技術のダメージが20%増加します</t>
   </si>
   <si>
+    <t>・スキル使用時、魔力を40消費して該当スキルのダメージ量20%増加</t>
+  </si>
+  <si>
     <t>・기술로 적을 3 회 타격 시 대상에게 잿더미 효과 적용</t>
   </si>
   <si>
@@ -121,6 +137,9 @@
   </si>
   <si>
     <t>・技術を3回ヒットすると、ターゲットに灰燼効果を適用します</t>
+  </si>
+  <si>
+    <t>　敵を3回打撃時、対象に灰の山効果適用</t>
   </si>
   <si>
     <t>・잿더미</t>
@@ -128,7 +147,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="409.55"/>
+        <sz val="409"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ ゴシック"/>
         <family val="3"/>
@@ -137,7 +156,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="409.55"/>
+        <sz val="409"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -149,15 +168,24 @@
     <t>・残り火</t>
   </si>
   <si>
+    <t>・灰の山</t>
+  </si>
+  <si>
     <t>　・Damage received from Adventurers +15% for 5 seconds</t>
   </si>
   <si>
+    <t>　5秒間、冒険者から受けるダメージ量15%増加</t>
+  </si>
+  <si>
     <t>　・200 burn damage every second for 5 seconds</t>
+  </si>
+  <si>
+    <t>　5秒間、毎秒200の火傷ダメージ</t>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="409.55"/>
+        <sz val="409"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ ゴシック"/>
         <family val="3"/>
@@ -166,7 +194,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="409.55"/>
+        <sz val="409"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -175,7 +203,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="409.55"/>
+        <sz val="409"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ ゴシック"/>
         <family val="3"/>
@@ -184,1105 +212,12 @@
     </r>
   </si>
   <si>
-    <t>　・(Cooldown: 30 seconds)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Oblivion</t>
-    </r>
-  </si>
-  <si>
-    <t>　・Unable to restore MP and combat resources, and DP -150 for 7 seconds</t>
-  </si>
-  <si>
-    <t>　・Unable to use Evasion for 2 seconds</t>
-  </si>
-  <si>
-    <t>　・Oblivion users are immune to the Oblivion effect</t>
-  </si>
-  <si>
-    <t>베디안트</t>
-  </si>
-  <si>
-    <t>Vediant</t>
-  </si>
-  <si>
-    <t>ベディアント</t>
-  </si>
-  <si>
-    <t>베디안트에서 환영검을 소환하여 원거리에서 적을 끊임없이 유린한다.</t>
-  </si>
-  <si>
-    <t>Summons Phantom Blades from the Vediant to constantly harass enemies from a distance.</t>
-  </si>
-  <si>
-    <t>ベディアントからファントム ブレードを召喚し、遠くから敵を継続的に攻撃します。</t>
-  </si>
-  <si>
-    <t>・마력이 100 일 경우 기술 사용 시 마력 50 을 소모하여 10 초간 비산하는 어둠 상태 적용</t>
-  </si>
-  <si>
-    <t>・When Mana is 100 , consumes 50 Mana upon using skill to apply Scattering Darkness state for 10 sec</t>
-  </si>
-  <si>
-    <t>・魔力が 100 の場合、技術使用時に 50 魔力を消費して 10 秒間散乱闇状態を適用します</t>
-  </si>
-  <si>
-    <t>・비산하는 어둠</t>
-  </si>
-  <si>
-    <t>・Scattering Darkness</t>
-  </si>
-  <si>
-    <t>・散る闇</t>
-  </si>
-  <si>
-    <t>　・기술 사용 시 환영검 을 소환</t>
-  </si>
-  <si>
-    <t>　・Summons Phantom Blades upon using skill</t>
-  </si>
-  <si>
-    <t>　・技術使用時にファントムブレードを召喚</t>
-  </si>
-  <si>
-    <t>　・최대 3 타격</t>
-  </si>
-  <si>
-    <t>　・Max 3 hits</t>
-  </si>
-  <si>
-    <t>　・最大3ヒット</t>
-  </si>
-  <si>
-    <t>　・10초 간 1초 마다 마력 12 소모</t>
-  </si>
-  <si>
-    <t>　・Consumes 12 Mana every 1 seconds for 10 seconds</t>
-  </si>
-  <si>
-    <t>　・10秒間、1秒ごとに12魔力を消費</t>
-  </si>
-  <si>
-    <t>・기술 첫 타격 성공 시 대상에게 망각 효과 적용</t>
-  </si>
-  <si>
-    <t>・Applies Oblivion effect to target upon successful first hit</t>
-  </si>
-  <si>
-    <t>・最初のヒットが成功したときにターゲットにオブリビオン効果を適用します</t>
-  </si>
-  <si>
-    <t>　・(재사용 대기 시간 30초 )</t>
-  </si>
-  <si>
-    <t>　・(Cooldown: 30 seconds )</t>
-  </si>
-  <si>
-    <t>　・(再使用待機時間: 30秒)</t>
-  </si>
-  <si>
-    <t>・망각</t>
-  </si>
-  <si>
-    <t>・オブリビオン</t>
-  </si>
-  <si>
-    <t>　・7초 동안 정신력 및 전투자원의 회복 불가 및 방어력 150 감소</t>
-  </si>
-  <si>
-    <t>　・精神力と戦闘リソースを回復できなくなり、7秒間DP-150</t>
-  </si>
-  <si>
-    <t>　・2초 동안 회피 사용 불가능</t>
-  </si>
-  <si>
-    <t>　・2秒間回避が使用できなくなります</t>
-  </si>
-  <si>
-    <t>　・망각 사용자의 경우 망각 효과 면역</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-      </rPr>
-      <t>　・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Oblivion </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-      </rPr>
-      <t>ユーザーは</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Oblivion </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="409.55"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-      </rPr>
-      <t>効果の影響を受けません</t>
-    </r>
-  </si>
-  <si>
-    <t>태도 수련</t>
-  </si>
-  <si>
-    <t>Kriegsmesser Training</t>
-  </si>
-  <si>
-    <t>太刀修練</t>
-  </si>
-  <si>
-    <t>태도 수련의 피해량이 증가한다.</t>
-  </si>
-  <si>
-    <t>Kriegsmesser Training damage increases.</t>
-  </si>
-  <si>
-    <t>太刀トレーニングのダメージが増加します。</t>
-  </si>
-  <si>
-    <t>・최대 사용 횟수 : 1</t>
-  </si>
-  <si>
-    <t>・Max Uses: 1</t>
-  </si>
-  <si>
-    <t>・最大使用回数: 1</t>
-  </si>
-  <si>
-    <t>・타격 시 마력 회복 7</t>
-  </si>
-  <si>
-    <t>・Restores 7 Mana upon hit</t>
-  </si>
-  <si>
-    <t>・ヒット時に7魔力回復</t>
-  </si>
-  <si>
-    <t>할퀴는 광기</t>
-  </si>
-  <si>
-    <t>Raking Madness</t>
-  </si>
-  <si>
-    <t>引き裂く狂気</t>
-  </si>
-  <si>
-    <t>PvE ｜계열 무결 선명한 정돈된</t>
-  </si>
-  <si>
-    <t>PvE ｜Branch Aal Serrett Labreve</t>
-  </si>
-  <si>
-    <t>PvE ｜系列 無欠 鮮明한 洗練された</t>
-  </si>
-  <si>
-    <t>어두운 기운을 휘감으며 태도로 연속 공격을 한다.</t>
-  </si>
-  <si>
-    <t>Performs a continuous attack with the Kriegsmesser while surrounded by dark energy.</t>
-  </si>
-  <si>
-    <t>暗黒のエネルギーに包まれながら太刀で連続攻撃を行う。</t>
-  </si>
-  <si>
-    <t>・최대 사용 횟수 : 2</t>
-  </si>
-  <si>
-    <t>・Max Uses: 2</t>
-  </si>
-  <si>
-    <t>・最大使用回数: 2</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 4초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 4 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 4秒</t>
-  </si>
-  <si>
-    <t>・최대 2 타격</t>
-  </si>
-  <si>
-    <t>・Max 2 hits</t>
-  </si>
-  <si>
-    <t>・最大2ヒット</t>
-  </si>
-  <si>
-    <t>・기술 사용 중 슈퍼 아머 , 잡기 불가</t>
-  </si>
-  <si>
-    <t>・Super Armor , Grab Immunity while using skill</t>
-  </si>
-  <si>
-    <t>・スーパーアーマー、技術使用中に免疫を獲得</t>
-  </si>
-  <si>
-    <t>・타격 성공 시 기절</t>
-  </si>
-  <si>
-    <t>・Stun on successful hit</t>
-  </si>
-  <si>
-    <t>・ヒット成功時に気絶させる</t>
-  </si>
-  <si>
-    <t>정령의 유산</t>
-  </si>
-  <si>
-    <t>Spirit's Legacy</t>
-  </si>
-  <si>
-    <t>精霊の遺産</t>
-  </si>
-  <si>
-    <t>ラストブレス</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜계열 수호 선명한 정돈된</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜Branch Aal Serrett Labreve</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜系列 守護 鮮明한 洗練された</t>
-  </si>
-  <si>
-    <t>전방의 적에게 환영검에 강력한 마력을 담아 터트린다.</t>
-  </si>
-  <si>
-    <t>Infuses powerful magic into Phantom Blades to detonate them on enemies in front.</t>
-  </si>
-  <si>
-    <t>ファントムブレードに強力な魔法を注入し、前方の敵を爆発させます。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 6초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 6 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 6秒</t>
-  </si>
-  <si>
-    <t>・공격 중 슈퍼 아머</t>
-  </si>
-  <si>
-    <t>・Super Armor during attack</t>
-  </si>
-  <si>
-    <t>・攻撃時スーパーアーマー</t>
-  </si>
-  <si>
-    <t>・기술 사용 지점에 2초 간 유지되는 어둠의 장막 생성</t>
-  </si>
-  <si>
-    <t>・Creates Dark Veil that lasts for 2 seconds at skill's location</t>
-  </si>
-  <si>
-    <t>・技術の位置に2秒間持続するダークベールを作成します</t>
-  </si>
-  <si>
-    <t>운명의 수레바퀴</t>
-  </si>
-  <si>
-    <t>Wheel of Fate</t>
-  </si>
-  <si>
-    <t>運命の輪</t>
-  </si>
-  <si>
-    <t>ギアーズオブフェイト</t>
-  </si>
-  <si>
-    <t>태도에 힘을 응축시켜 어둠의 검기를 사방으로 흩뿌린다.</t>
-  </si>
-  <si>
-    <t>Concentrates power in the Kriegsmesser and scatters dark sword energy in all directions.</t>
-  </si>
-  <si>
-    <t>太刀に力を集中させ、暗黒の剣のエネルギーを四方八方に撒き散らす。</t>
-  </si>
-  <si>
-    <t>・기술 사용 중 슈퍼 아머</t>
-  </si>
-  <si>
-    <t>・Super Armor while using skill</t>
-  </si>
-  <si>
-    <t>・技術使用時のスーパーアーマー</t>
-  </si>
-  <si>
-    <t>・타격 성공 시 넉백</t>
-  </si>
-  <si>
-    <t>・Knockback on successful hit</t>
-  </si>
-  <si>
-    <t>・ヒット成功時のノックバック</t>
-  </si>
-  <si>
-    <t>착취의 손길</t>
-  </si>
-  <si>
-    <t>Grip of Exploitation</t>
-  </si>
-  <si>
-    <t>搾取の手</t>
-  </si>
-  <si>
-    <t>血の宴</t>
-  </si>
-  <si>
-    <t>PvP ｜계열 찬란한 무결한 선명한</t>
-  </si>
-  <si>
-    <t>PvP ｜Branch Elion Aal Serrett</t>
-  </si>
-  <si>
-    <t>PvP ｜系列 燦爛 無欠한 鮮明한</t>
-  </si>
-  <si>
-    <t>전방에 지면을 타는 광역 마법 공격을 한다.</t>
-  </si>
-  <si>
-    <t>Performs a wide-area magic attack that crawls along the ground in front.</t>
-  </si>
-  <si>
-    <t>前方の地面を這う広範囲魔法攻撃を行う。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 7초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 7 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 7秒</t>
-  </si>
-  <si>
-    <t>・기술 버튼 유지 시 최대 2 타격</t>
-  </si>
-  <si>
-    <t>・Max 2 hits when holding the skill button</t>
-  </si>
-  <si>
-    <t>・技術ボタン長押しで最大2ヒット</t>
-  </si>
-  <si>
-    <t>・즉시 발동 기술</t>
-  </si>
-  <si>
-    <t>・Instant Activation Skill</t>
-  </si>
-  <si>
-    <t>・即時発動技術</t>
-  </si>
-  <si>
-    <t>・타격 성공 시 넉다운</t>
-  </si>
-  <si>
-    <t>・Knockdown on successful hit</t>
-  </si>
-  <si>
-    <t>・ヒット成功時のノックダウン</t>
-  </si>
-  <si>
-    <t>・이동 공격 가능</t>
-  </si>
-  <si>
-    <t>・Movement attack possible</t>
-  </si>
-  <si>
-    <t>・移動攻撃可能</t>
-  </si>
-  <si>
-    <t>급습</t>
-  </si>
-  <si>
-    <t>Ambush</t>
-  </si>
-  <si>
-    <t>急襲</t>
-  </si>
-  <si>
-    <t>PvP ｜계열 무결한 선명한 정돈된</t>
-  </si>
-  <si>
-    <t>PvP ｜Branch Aal Serrett Labreve</t>
-  </si>
-  <si>
-    <t>PvP ｜系列 無欠한 鮮明한 洗練された</t>
-  </si>
-  <si>
-    <t>순간적으로 적에게 접근하여 적을 가격한다.</t>
-  </si>
-  <si>
-    <t>Instantly approaches and strikes the enemy.</t>
-  </si>
-  <si>
-    <t>瞬時に敵に接近し攻撃する。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 4.7초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 4.7 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 4.7秒</t>
-  </si>
-  <si>
-    <t>・타격 성공 시 경직</t>
-  </si>
-  <si>
-    <t>・Stiffness on successful hit</t>
-  </si>
-  <si>
-    <t>・ヒット成功時の硬さ</t>
-  </si>
-  <si>
-    <t>갈라지는 어둠</t>
-  </si>
-  <si>
-    <t>Splitting Darkness</t>
-  </si>
-  <si>
-    <t>裂ける闇</t>
-  </si>
-  <si>
-    <t>スラッシュダークネス</t>
-  </si>
-  <si>
-    <t>PvE ｜계열 무결한 정돈된 희미한</t>
-  </si>
-  <si>
-    <t>PvE ｜Branch Aal Labreve Ahib</t>
-  </si>
-  <si>
-    <t>PvE ｜系列 無欠한 洗練された かすかな</t>
-  </si>
-  <si>
-    <t>강력한 마력을 담은 환영검을 소환하여 피해를 준다.</t>
-  </si>
-  <si>
-    <t>Summons Phantom Blades infused with powerful magic to deal damage.</t>
-  </si>
-  <si>
-    <t>強力な魔法が注入されたファントムブレードを召喚してダメージを与えます。</t>
-  </si>
-  <si>
-    <t>카마실비아의 참</t>
-  </si>
-  <si>
-    <t>Kamasylvia Slash</t>
-  </si>
-  <si>
-    <t>カーマスリビア斬り</t>
-  </si>
-  <si>
-    <t>カーマスリビアの魅了</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜계열 수호 무결한 선명한</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜Branch Aal Aal Serrett</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜系列 守護 無欠한 鮮明한</t>
-  </si>
-  <si>
-    <t>정령을 태워 얻은 응축된 힘을 참격에 실어 방출한다.</t>
-  </si>
-  <si>
-    <t>Releases concentrated power obtained by burning spirits in a slash.</t>
-  </si>
-  <si>
-    <t>魂を燃やして得た凝縮した力を斬撃に放つ。</t>
-  </si>
-  <si>
-    <t>빗발치는 절망</t>
-  </si>
-  <si>
-    <t>Raining Despair</t>
-  </si>
-  <si>
-    <t>降り注ぐ絶望</t>
-  </si>
-  <si>
-    <t>ディスペアーアーツ</t>
-  </si>
-  <si>
-    <t>PvP ｜계열 수호 무결한 정돈된</t>
-  </si>
-  <si>
-    <t>PvP ｜Branch Aal Aal Labreve</t>
-  </si>
-  <si>
-    <t>PvP ｜系列 守護 無欠한 洗練された</t>
-  </si>
-  <si>
-    <t>환영검을 던져 적에게 강력한 피해를 준다.</t>
-  </si>
-  <si>
-    <t>Throws Phantom Blades to deal powerful damage to enemies.</t>
-  </si>
-  <si>
-    <t>ファントムブレードを投げて敵に強力なダメージを与える。</t>
-  </si>
-  <si>
-    <t>・기술 사용 중 전방 가드</t>
-  </si>
-  <si>
-    <t>・Forward Guard while using skill</t>
-  </si>
-  <si>
-    <t>・技術使用中の前衛ガード</t>
-  </si>
-  <si>
-    <t>칠흑의 잿더미</t>
-  </si>
-  <si>
-    <t>Pitch-Black Ember</t>
-  </si>
-  <si>
-    <t>漆黒の灰</t>
-  </si>
-  <si>
-    <t>PvE ｜계열 수호 무결한 선명한</t>
-  </si>
-  <si>
-    <t>PvE ｜Branch Aal Aal Serrett</t>
-  </si>
-  <si>
-    <t>PvE ｜系列 守護 無欠한 鮮明한</t>
-  </si>
-  <si>
-    <t>태도에 모인 어둠의 기운을 강력히 휘둘러 방출시킨다.</t>
-  </si>
-  <si>
-    <t>Strongly wields and releases dark energy gathered in the Kriegsmesser.</t>
-  </si>
-  <si>
-    <t>太刀に集められた暗黒エネルギーを強力に操り、放出する。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 5.6초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 5.6 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 5.6秒</t>
-  </si>
-  <si>
-    <t>・Using Skill Super Armor</t>
-  </si>
-  <si>
-    <t>・技術スーパーアーマーの使用方法</t>
-  </si>
-  <si>
-    <t>재앙의 씨앗</t>
-  </si>
-  <si>
-    <t>Seed of Disaster</t>
-  </si>
-  <si>
-    <t>災厄の種</t>
-  </si>
-  <si>
-    <t>憎悪の種</t>
-  </si>
-  <si>
-    <t>적에게 마력의 환영을 소환하여 공격한다.</t>
-  </si>
-  <si>
-    <t>Summons a magical illusion to attack the enemy.</t>
-  </si>
-  <si>
-    <t>魔法の幻想を召喚して敵を攻撃します。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 8.8초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 8.8 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 8.8秒</t>
-  </si>
-  <si>
-    <t>・타격 성공 시 띄우기</t>
-  </si>
-  <si>
-    <t>・Knock-up on successful hit</t>
-  </si>
-  <si>
-    <t>・ヒット成功で浮かせ</t>
-  </si>
-  <si>
-    <t>베디르의 광기</t>
-  </si>
-  <si>
-    <t>Vedir's Madness</t>
-  </si>
-  <si>
-    <t>ベディルの狂気</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜계열 무결 정돈된 희미한</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜Branch Aal Labreve Ahib</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜系列 無欠 洗練された かすかな</t>
-  </si>
-  <si>
-    <t>어두운 기운을 모아 바닥에 태도를 내리 꽃으며 상대를 공격한다.</t>
-  </si>
-  <si>
-    <t>Gather dark energy and slam the Kriegsmesser into the ground to attack the opponent.</t>
-  </si>
-  <si>
-    <t>闇のエネルギーを集めて太刀を地面に叩きつけて相手を攻撃します。</t>
-  </si>
-  <si>
-    <t>황혼의 질주</t>
-  </si>
-  <si>
-    <t>Twilight Sprint</t>
-  </si>
-  <si>
-    <t>黄昏の疾走</t>
-  </si>
-  <si>
-    <t>ファントムチャージ</t>
-  </si>
-  <si>
-    <t>PvP ｜계열 무결 선명한 정돈된</t>
-  </si>
-  <si>
-    <t>PvP ｜系列 無欠 鮮明한 洗練された</t>
-  </si>
-  <si>
-    <t>전방으로 돌진하며 지나간 자리에 피해를 준다.</t>
-  </si>
-  <si>
-    <t>Dashes forward and deals damage in her wake.</t>
-  </si>
-  <si>
-    <t>前方にダッシュし、その後にダメージを与えます。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 6.4초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 6.4 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 6.4秒</t>
-  </si>
-  <si>
-    <t>・최대 11 타격</t>
-  </si>
-  <si>
-    <t>・Max 11 hits</t>
-  </si>
-  <si>
-    <t>・最大11ヒット</t>
-  </si>
-  <si>
-    <t>정령 포식</t>
-  </si>
-  <si>
-    <t>Spirit Devour</t>
-  </si>
-  <si>
-    <t>精霊捕食</t>
-  </si>
-  <si>
-    <t>精霊飽食</t>
-  </si>
-  <si>
-    <t>정령을 불태운 힘을 흡수하여 자신을 치유한다.</t>
-  </si>
-  <si>
-    <t>Absorbs power from burning spirits to heal oneself.</t>
-  </si>
-  <si>
-    <t>燃え盛る精霊の力を吸収して自身を回復する。</t>
-  </si>
-  <si>
-    <t>・10초 간 2초 마다 생명력 회복 115~400</t>
-  </si>
-  <si>
-    <t>・Restores 115~400 HP every 2 seconds for 10 seconds</t>
-  </si>
-  <si>
-    <t>・10秒間、2秒ごとに115〜400の生命力を回復します</t>
-  </si>
-  <si>
-    <t>・30초 간 공격력 +43~100</t>
-  </si>
-  <si>
-    <t>・AP +43~100 for 30 seconds</t>
-  </si>
-  <si>
-    <t>・30秒間AP +43~100</t>
-  </si>
-  <si>
-    <t>・30초 간 방어력 +43~100</t>
-  </si>
-  <si>
-    <t>・DP +43~100 for 30 seconds</t>
-  </si>
-  <si>
-    <t>・30秒間DP+43~100</t>
-  </si>
-  <si>
-    <t>・30초 간 치명타 피해량 +50%</t>
-  </si>
-  <si>
-    <t>・Critical Hit Damage +50% for 30 seconds</t>
-  </si>
-  <si>
-    <t>・30秒間致命打被害量+50%</t>
-  </si>
-  <si>
-    <t>・30초 간 흑정령 기술 피해량 +20%</t>
-  </si>
-  <si>
-    <t>・Black Spirit Skill Damage +20% for 30 seconds</t>
-  </si>
-  <si>
-    <t>・30秒間、闇の精霊技術被害量+20%</t>
-  </si>
-  <si>
-    <t>・기술 사용 시 30초 간 회피 기술 재사용 시간 2초 감소</t>
-  </si>
-  <si>
-    <t>・Evasion Cooldown -2 seconds for 30 seconds upon using skill</t>
-  </si>
-  <si>
-    <t>・技術使用時、30秒間回避再使用待機時間-2秒</t>
-  </si>
-  <si>
-    <t>피어나는 검은 장미</t>
-  </si>
-  <si>
-    <t>Blooming Black Rose</t>
-  </si>
-  <si>
-    <t>咲き誇る黒い薔薇</t>
-  </si>
-  <si>
-    <t>ブルーミングローズ</t>
-  </si>
-  <si>
-    <t>어두운 자연의 기운을 퍼뜨리고, 검은 장미를 피워낸다.</t>
-  </si>
-  <si>
-    <t>Spreads dark nature energy and blooms black roses.</t>
-  </si>
-  <si>
-    <t>闇の自然エネルギーをまき散らし、黒い薔薇を咲かせる。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 16초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 16 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 16秒</t>
-  </si>
-  <si>
-    <t>추락하는 신념</t>
-  </si>
-  <si>
-    <t>Crumbling Faith</t>
-  </si>
-  <si>
-    <t>崩れ落ちる信念</t>
-  </si>
-  <si>
-    <t>墜落する信念</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜계열 무결 선명한 정돈된</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜系列 無欠 鮮明한 洗練された</t>
-  </si>
-  <si>
-    <t>후방으로 도약하며 전방에 환영검을 던져 피해를 입힌다.</t>
-  </si>
-  <si>
-    <t>Leaps backward and throws Phantom Blades forward to deal damage.</t>
-  </si>
-  <si>
-    <t>後方に飛び上がり、ファントムブレードを前方に投げてダメージを与えます。</t>
-  </si>
-  <si>
-    <t>・재사용 대기시간 : 15초</t>
-  </si>
-  <si>
-    <t>・Cooldown: 15 seconds</t>
-  </si>
-  <si>
-    <t>・再使用待機時間: 15秒</t>
-  </si>
-  <si>
-    <t>・기술 사용 중 슈퍼 아머 , 피해 감소 , 잡기 불가</t>
-  </si>
-  <si>
-    <t>・Super Armor , Damage Reduction , Grab Immunity while using skill</t>
-  </si>
-  <si>
-    <t>・スーパーアーマー、被害減少、技術使用時の獲得免疫</t>
-  </si>
-  <si>
-    <t>기울어진 균형</t>
-  </si>
-  <si>
-    <t>Tilted Balance</t>
-  </si>
-  <si>
-    <t>傾いた均衡</t>
-  </si>
-  <si>
-    <t>インバランス</t>
-  </si>
-  <si>
-    <t>대지를 흔들며 어두운 기운을 방출하여 전방의 적에게 강한 충격을 준다.</t>
-  </si>
-  <si>
-    <t>Shakes the earth and releases dark energy to deliver a strong shock to enemies in front.</t>
-  </si>
-  <si>
-    <t>大地を揺るがし暗黒のエネルギーを放出し、前方の敵に強烈な衝撃を与える。</t>
-  </si>
-  <si>
-    <t>어두운 별구름</t>
-  </si>
-  <si>
-    <t>Dark Star Cloud</t>
-  </si>
-  <si>
-    <t>暗い星雲</t>
-  </si>
-  <si>
-    <t>暗然たる雨雲</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜계열 수호 무결 선명한</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜系列 守護 無欠 鮮明한</t>
-  </si>
-  <si>
-    <t>응어리진 어둠의 기운을 터트려 적을 공격한다.</t>
-  </si>
-  <si>
-    <t>Explodes pent-up dark energy to attack enemies.</t>
-  </si>
-  <si>
-    <t>溜まった暗黒エネルギーを爆発させて敵を攻撃します。</t>
-  </si>
-  <si>
-    <t>흑정령의 분노</t>
-  </si>
-  <si>
-    <t>Black Spirit's Rage</t>
-  </si>
-  <si>
-    <t>黒精霊の怒り</t>
-  </si>
-  <si>
-    <t>전방에 흑정령의 기운과 마력을 한 곳에 모아 폭발시킨다.</t>
-  </si>
-  <si>
-    <t>Gathers Black Spirit's energy and Mana in one place in front and detonates it.</t>
-  </si>
-  <si>
-    <t>闇の精霊のエネルギーと魔力を前方一箇所に集めて爆発させる。</t>
-  </si>
-  <si>
-    <t>・기술 사용 중 슈퍼 아머 , 피해 감소</t>
-  </si>
-  <si>
-    <t>・Super Armor , Damage Reduction while using skill</t>
-  </si>
-  <si>
-    <t>・スーパーアーマー、技術使用時の被害減少</t>
-  </si>
-  <si>
-    <t>・무기 선택 : 태도 적용시</t>
-  </si>
-  <si>
-    <t>・When Weapon Selection: Kriegsmesser is applied</t>
-  </si>
-  <si>
-    <t>・武器選択：太刀適用時</t>
-  </si>
-  <si>
-    <t>・최대 6 타격</t>
-  </si>
-  <si>
-    <t>・Max 6 hits</t>
-  </si>
-  <si>
-    <t>・最大6ヒット</t>
-  </si>
-  <si>
-    <t>・무기 선택 : 베디안트 적용시</t>
-  </si>
-  <si>
-    <t>・When Weapon Selection: Vediant is applied</t>
-  </si>
-  <si>
-    <t>・武器選択：ベディアント適用時</t>
-  </si>
-  <si>
-    <t>・최대 5 타격</t>
-  </si>
-  <si>
-    <t>・Max 5 hits</t>
-  </si>
-  <si>
-    <t>・最大5ヒット</t>
-  </si>
-  <si>
-    <t>・타격 성공 시 바운드</t>
-  </si>
-  <si>
-    <t>・Bound on successful hit</t>
-  </si>
-  <si>
-    <t>・ヒット成功時にバインドされる</t>
-  </si>
-  <si>
-    <t>太刀を振るい、闇の魔法と巧みな剣術で敵を容赦なく斬り伏せる。</t>
-  </si>
-  <si>
-    <t>・攻撃された時、3秒間冒険者から受けるダメージ量50%減少</t>
-  </si>
-  <si>
-    <t>（再使用待機時間15秒）</t>
-  </si>
-  <si>
-    <t>・スキル使用時、魔力12回復</t>
-  </si>
-  <si>
-    <t>・スキル使用時、魔力を40消費して該当スキルのダメージ量20%増加</t>
-  </si>
-  <si>
-    <t>　敵を3回打撃時、対象に灰の山効果適用</t>
-  </si>
-  <si>
-    <t>・灰の山</t>
-  </si>
-  <si>
-    <t>　5秒間、冒険者から受けるダメージ量15%増加</t>
-  </si>
-  <si>
-    <t>　5秒間、毎秒200の火傷ダメージ</t>
-  </si>
-  <si>
-    <t>・スキル1回目の打撃成功時、対象に忘却効果適用</t>
-  </si>
-  <si>
-    <t>（再使用待機時間30秒）</t>
-  </si>
-  <si>
-    <t>　忘却</t>
-  </si>
-  <si>
-    <t>　7秒間、MPおよび戦闘資源の回復不可、防御力150減少</t>
-  </si>
-  <si>
-    <t>　2秒間、回避使用不可</t>
-  </si>
-  <si>
-    <t>　忘却を使用できるクラスは、忘却効果耐性</t>
-  </si>
-  <si>
-    <t>ベディアントから幻影剣を召喚し、遠距離から敵を絶え間なく蹂躙する。</t>
-  </si>
-  <si>
-    <t>・魔力が100の場合、スキル使用時、魔力を50消費して10秒間、壊刃の精状態適用</t>
-  </si>
-  <si>
-    <t>・壊刃の精</t>
-  </si>
-  <si>
-    <t>　スキル使用時、幻影剣を召喚
-　打撃ダメージ800%適用
-　PVP打撃ダメージ400%適用</t>
-  </si>
-  <si>
-    <t>　最大3打撃</t>
-  </si>
-  <si>
-    <t>　10秒間、1秒ごとに魔力12消費</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF2B2B2B"/>
         <rFont val="ＭＳ 明朝"/>
         <family val="1"/>
-        <charset val="128"/>
       </rPr>
       <t>・スキル</t>
     </r>
@@ -1300,10 +235,1234 @@
         <color rgb="FF2B2B2B"/>
         <rFont val="ＭＳ 明朝"/>
         <family val="1"/>
-        <charset val="128"/>
       </rPr>
       <t>回目の打撃成功時、対象に忘却効果適用</t>
     </r>
+  </si>
+  <si>
+    <t>　・(Cooldown: 30 seconds)</t>
+  </si>
+  <si>
+    <t>（再使用待機時間30秒）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="409"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="409"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Oblivion</t>
+    </r>
+  </si>
+  <si>
+    <t>　忘却</t>
+  </si>
+  <si>
+    <t>　・Unable to restore MP and combat resources, and DP -150 for 7 seconds</t>
+  </si>
+  <si>
+    <t>　7秒間、MPおよび戦闘資源の回復不可、防御力150減少</t>
+  </si>
+  <si>
+    <t>　・Unable to use Evasion for 2 seconds</t>
+  </si>
+  <si>
+    <t>　2秒間、回避使用不可</t>
+  </si>
+  <si>
+    <t>　・Oblivion users are immune to the Oblivion effect</t>
+  </si>
+  <si>
+    <t>　忘却を使用できるクラスは、忘却効果耐性</t>
+  </si>
+  <si>
+    <t>베디안트</t>
+  </si>
+  <si>
+    <t>Vediant</t>
+  </si>
+  <si>
+    <t>ベディアント</t>
+  </si>
+  <si>
+    <t>베디안트에서 환영검을 소환하여 원거리에서 적을 끊임없이 유린한다.</t>
+  </si>
+  <si>
+    <t>Summons Phantom Blades from the Vediant to constantly harass enemies from a distance.</t>
+  </si>
+  <si>
+    <t>ベディアントからファントム ブレードを召喚し、遠くから敵を継続的に攻撃します。</t>
+  </si>
+  <si>
+    <t>ベディアントから幻影剣を召喚し、遠距離から敵を絶え間なく蹂躙する。</t>
+  </si>
+  <si>
+    <t>・마력이 100 일 경우 기술 사용 시 마력 50 을 소모하여 10 초간 비산하는 어둠 상태 적용</t>
+  </si>
+  <si>
+    <t>・When Mana is 100 , consumes 50 Mana upon using skill to apply Scattering Darkness state for 10 sec</t>
+  </si>
+  <si>
+    <t>・魔力が 100 の場合、技術使用時に 50 魔力を消費して 10 秒間散乱闇状態を適用します</t>
+  </si>
+  <si>
+    <t>・魔力が100の場合、スキル使用時、魔力を50消費して10秒間、壊刃の精状態適用</t>
+  </si>
+  <si>
+    <t>・비산하는 어둠</t>
+  </si>
+  <si>
+    <t>・Scattering Darkness</t>
+  </si>
+  <si>
+    <t>・散る闇</t>
+  </si>
+  <si>
+    <t>・壊刃の精</t>
+  </si>
+  <si>
+    <t>　・기술 사용 시 환영검 을 소환</t>
+  </si>
+  <si>
+    <t>　・Summons Phantom Blades upon using skill</t>
+  </si>
+  <si>
+    <t>　・技術使用時にファントムブレードを召喚</t>
+  </si>
+  <si>
+    <t>　スキル使用時、幻影剣を召喚
+　打撃ダメージ800%適用
+　PVP打撃ダメージ400%適用</t>
+  </si>
+  <si>
+    <t>　・최대 3 타격</t>
+  </si>
+  <si>
+    <t>　・Max 3 hits</t>
+  </si>
+  <si>
+    <t>　・最大3ヒット</t>
+  </si>
+  <si>
+    <t>　最大3打撃</t>
+  </si>
+  <si>
+    <t>　・10초 간 1초 마다 마력 12 소모</t>
+  </si>
+  <si>
+    <t>　・Consumes 12 Mana every 1 seconds for 10 seconds</t>
+  </si>
+  <si>
+    <t>　・10秒間、1秒ごとに12魔力を消費</t>
+  </si>
+  <si>
+    <t>　10秒間、1秒ごとに魔力12消費</t>
+  </si>
+  <si>
+    <t>・기술 첫 타격 성공 시 대상에게 망각 효과 적용</t>
+  </si>
+  <si>
+    <t>・Applies Oblivion effect to target upon successful first hit</t>
+  </si>
+  <si>
+    <t>・最初のヒットが成功したときにターゲットにオブリビオン効果を適用します</t>
+  </si>
+  <si>
+    <t>・スキル1回目の打撃成功時、対象に忘却効果適用</t>
+  </si>
+  <si>
+    <t>　・(재사용 대기 시간 30초 )</t>
+  </si>
+  <si>
+    <t>　・(Cooldown: 30 seconds )</t>
+  </si>
+  <si>
+    <t>　・(再使用待機時間: 30秒)</t>
+  </si>
+  <si>
+    <t>・망각</t>
+  </si>
+  <si>
+    <t>・オブリビオン</t>
+  </si>
+  <si>
+    <t>　・7초 동안 정신력 및 전투자원의 회복 불가 및 방어력 150 감소</t>
+  </si>
+  <si>
+    <t>　・精神力と戦闘リソースを回復できなくなり、7秒間DP-150</t>
+  </si>
+  <si>
+    <t>　・2초 동안 회피 사용 불가능</t>
+  </si>
+  <si>
+    <t>　・2秒間回避が使用できなくなります</t>
+  </si>
+  <si>
+    <t>　・망각 사용자의 경우 망각 효과 면역</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="409"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+      </rPr>
+      <t>　・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="409"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Oblivion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="409"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+      </rPr>
+      <t>ユーザーは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="409"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Oblivion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="409"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+      </rPr>
+      <t>効果の影響を受けません</t>
+    </r>
+  </si>
+  <si>
+    <t>태도 수련</t>
+  </si>
+  <si>
+    <t>Kriegsmesser Training</t>
+  </si>
+  <si>
+    <t>太刀修練</t>
+  </si>
+  <si>
+    <t>태도 수련의 피해량이 증가한다.</t>
+  </si>
+  <si>
+    <t>Kriegsmesser Training damage increases.</t>
+  </si>
+  <si>
+    <t>太刀トレーニングのダメージが増加します。</t>
+  </si>
+  <si>
+    <t>・최대 사용 횟수 : 1</t>
+  </si>
+  <si>
+    <t>・Max Uses: 1</t>
+  </si>
+  <si>
+    <t>・最大使用回数: 1</t>
+  </si>
+  <si>
+    <t>・타격 시 마력 회복 7</t>
+  </si>
+  <si>
+    <t>・Restores 7 Mana upon hit</t>
+  </si>
+  <si>
+    <t>・ヒット時に7魔力回復</t>
+  </si>
+  <si>
+    <t>할퀴는 광기</t>
+  </si>
+  <si>
+    <t>Raking Madness</t>
+  </si>
+  <si>
+    <t>引き裂く狂気</t>
+  </si>
+  <si>
+    <t>PvE ｜계열 무결 선명한 정돈된</t>
+  </si>
+  <si>
+    <t>PvE ｜Branch Aal Serrett Labreve</t>
+  </si>
+  <si>
+    <t>PvE ｜系列 無欠 鮮明한 洗練された</t>
+  </si>
+  <si>
+    <t>어두운 기운을 휘감으며 태도로 연속 공격을 한다.</t>
+  </si>
+  <si>
+    <t>Performs a continuous attack with the Kriegsmesser while surrounded by dark energy.</t>
+  </si>
+  <si>
+    <t>暗黒のエネルギーに包まれながら太刀で連続攻撃を行う。</t>
+  </si>
+  <si>
+    <t>・최대 사용 횟수 : 2</t>
+  </si>
+  <si>
+    <t>・Max Uses: 2</t>
+  </si>
+  <si>
+    <t>・最大使用回数: 2</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 4초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 4 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 4秒</t>
+  </si>
+  <si>
+    <t>・최대 2 타격</t>
+  </si>
+  <si>
+    <t>・Max 2 hits</t>
+  </si>
+  <si>
+    <t>・最大2ヒット</t>
+  </si>
+  <si>
+    <t>・기술 사용 중 슈퍼 아머 , 잡기 불가</t>
+  </si>
+  <si>
+    <t>・Super Armor , Grab Immunity while using skill</t>
+  </si>
+  <si>
+    <t>・スーパーアーマー、技術使用中に免疫を獲得</t>
+  </si>
+  <si>
+    <t>・타격 성공 시 기절</t>
+  </si>
+  <si>
+    <t>・Stun on successful hit</t>
+  </si>
+  <si>
+    <t>・ヒット成功時に気絶させる</t>
+  </si>
+  <si>
+    <t>정령의 유산</t>
+  </si>
+  <si>
+    <t>Spirit's Legacy</t>
+  </si>
+  <si>
+    <t>精霊の遺産</t>
+  </si>
+  <si>
+    <t>ラストブレス</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜계열 수호 선명한 정돈된</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜Branch Aal Serrett Labreve</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜系列 守護 鮮明한 洗練された</t>
+  </si>
+  <si>
+    <t>전방의 적에게 환영검에 강력한 마력을 담아 터트린다.</t>
+  </si>
+  <si>
+    <t>Infuses powerful magic into Phantom Blades to detonate them on enemies in front.</t>
+  </si>
+  <si>
+    <t>ファントムブレードに強力な魔法を注入し、前方の敵を爆発させます。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 6초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 6 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 6秒</t>
+  </si>
+  <si>
+    <t>・공격 중 슈퍼 아머</t>
+  </si>
+  <si>
+    <t>・Super Armor during attack</t>
+  </si>
+  <si>
+    <t>・攻撃時スーパーアーマー</t>
+  </si>
+  <si>
+    <t>・기술 사용 지점에 2초 간 유지되는 어둠의 장막 생성</t>
+  </si>
+  <si>
+    <t>・Creates Dark Veil that lasts for 2 seconds at skill's location</t>
+  </si>
+  <si>
+    <t>・技術の位置に2秒間持続するダークベールを作成します</t>
+  </si>
+  <si>
+    <t>운명의 수레바퀴</t>
+  </si>
+  <si>
+    <t>Wheel of Fate</t>
+  </si>
+  <si>
+    <t>運命の輪</t>
+  </si>
+  <si>
+    <t>ギアーズオブフェイト</t>
+  </si>
+  <si>
+    <t>태도에 힘을 응축시켜 어둠의 검기를 사방으로 흩뿌린다.</t>
+  </si>
+  <si>
+    <t>Concentrates power in the Kriegsmesser and scatters dark sword energy in all directions.</t>
+  </si>
+  <si>
+    <t>太刀に力を集中させ、暗黒の剣のエネルギーを四方八方に撒き散らす。</t>
+  </si>
+  <si>
+    <t>・기술 사용 중 슈퍼 아머</t>
+  </si>
+  <si>
+    <t>・Super Armor while using skill</t>
+  </si>
+  <si>
+    <t>・技術使用時のスーパーアーマー</t>
+  </si>
+  <si>
+    <t>・타격 성공 시 넉백</t>
+  </si>
+  <si>
+    <t>・Knockback on successful hit</t>
+  </si>
+  <si>
+    <t>・ヒット成功時のノックバック</t>
+  </si>
+  <si>
+    <t>착취의 손길</t>
+  </si>
+  <si>
+    <t>Grip of Exploitation</t>
+  </si>
+  <si>
+    <t>搾取の手</t>
+  </si>
+  <si>
+    <t>血の宴</t>
+  </si>
+  <si>
+    <t>PvP ｜계열 찬란한 무결한 선명한</t>
+  </si>
+  <si>
+    <t>PvP ｜Branch Elion Aal Serrett</t>
+  </si>
+  <si>
+    <t>PvP ｜系列 燦爛 無欠한 鮮明한</t>
+  </si>
+  <si>
+    <t>전방에 지면을 타는 광역 마법 공격을 한다.</t>
+  </si>
+  <si>
+    <t>Performs a wide-area magic attack that crawls along the ground in front.</t>
+  </si>
+  <si>
+    <t>前方の地面を這う広範囲魔法攻撃を行う。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 7초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 7 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 7秒</t>
+  </si>
+  <si>
+    <t>・기술 버튼 유지 시 최대 2 타격</t>
+  </si>
+  <si>
+    <t>・Max 2 hits when holding the skill button</t>
+  </si>
+  <si>
+    <t>・技術ボタン長押しで最大2ヒット</t>
+  </si>
+  <si>
+    <t>・즉시 발동 기술</t>
+  </si>
+  <si>
+    <t>・Instant Activation Skill</t>
+  </si>
+  <si>
+    <t>・即時発動技術</t>
+  </si>
+  <si>
+    <t>・타격 성공 시 넉다운</t>
+  </si>
+  <si>
+    <t>・Knockdown on successful hit</t>
+  </si>
+  <si>
+    <t>・ヒット成功時のノックダウン</t>
+  </si>
+  <si>
+    <t>・이동 공격 가능</t>
+  </si>
+  <si>
+    <t>・Movement attack possible</t>
+  </si>
+  <si>
+    <t>・移動攻撃可能</t>
+  </si>
+  <si>
+    <t>급습</t>
+  </si>
+  <si>
+    <t>Ambush</t>
+  </si>
+  <si>
+    <t>急襲</t>
+  </si>
+  <si>
+    <t>PvP ｜계열 무결한 선명한 정돈된</t>
+  </si>
+  <si>
+    <t>PvP ｜Branch Aal Serrett Labreve</t>
+  </si>
+  <si>
+    <t>PvP ｜系列 無欠한 鮮明한 洗練された</t>
+  </si>
+  <si>
+    <t>순간적으로 적에게 접근하여 적을 가격한다.</t>
+  </si>
+  <si>
+    <t>Instantly approaches and strikes the enemy.</t>
+  </si>
+  <si>
+    <t>瞬時に敵に接近し攻撃する。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 4.7초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 4.7 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 4.7秒</t>
+  </si>
+  <si>
+    <t>・타격 성공 시 경직</t>
+  </si>
+  <si>
+    <t>・Stiffness on successful hit</t>
+  </si>
+  <si>
+    <t>・ヒット成功時の硬さ</t>
+  </si>
+  <si>
+    <t>갈라지는 어둠</t>
+  </si>
+  <si>
+    <t>Splitting Darkness</t>
+  </si>
+  <si>
+    <t>裂ける闇</t>
+  </si>
+  <si>
+    <t>スラッシュダークネス</t>
+  </si>
+  <si>
+    <t>PvE ｜계열 무결한 정돈된 희미한</t>
+  </si>
+  <si>
+    <t>PvE ｜Branch Aal Labreve Ahib</t>
+  </si>
+  <si>
+    <t>PvE ｜系列 無欠한 洗練された かすかな</t>
+  </si>
+  <si>
+    <t>강력한 마력을 담은 환영검을 소환하여 피해를 준다.</t>
+  </si>
+  <si>
+    <t>Summons Phantom Blades infused with powerful magic to deal damage.</t>
+  </si>
+  <si>
+    <t>強力な魔法が注入されたファントムブレードを召喚してダメージを与えます。</t>
+  </si>
+  <si>
+    <t>카마실비아의 참</t>
+  </si>
+  <si>
+    <t>Kamasylvia Slash</t>
+  </si>
+  <si>
+    <t>カーマスリビア斬り</t>
+  </si>
+  <si>
+    <t>カーマスリビアの魅了</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜계열 수호 무결한 선명한</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜Branch Aal Aal Serrett</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜系列 守護 無欠한 鮮明한</t>
+  </si>
+  <si>
+    <t>정령을 태워 얻은 응축된 힘을 참격에 실어 방출한다.</t>
+  </si>
+  <si>
+    <t>Releases concentrated power obtained by burning spirits in a slash.</t>
+  </si>
+  <si>
+    <t>魂を燃やして得た凝縮した力を斬撃に放つ。</t>
+  </si>
+  <si>
+    <t>빗발치는 절망</t>
+  </si>
+  <si>
+    <t>Raining Despair</t>
+  </si>
+  <si>
+    <t>降り注ぐ絶望</t>
+  </si>
+  <si>
+    <t>ディスペアーアーツ</t>
+  </si>
+  <si>
+    <t>PvP ｜계열 수호 무결한 정돈된</t>
+  </si>
+  <si>
+    <t>PvP ｜Branch Aal Aal Labreve</t>
+  </si>
+  <si>
+    <t>PvP ｜系列 守護 無欠한 洗練された</t>
+  </si>
+  <si>
+    <t>환영검을 던져 적에게 강력한 피해를 준다.</t>
+  </si>
+  <si>
+    <t>Throws Phantom Blades to deal powerful damage to enemies.</t>
+  </si>
+  <si>
+    <t>ファントムブレードを投げて敵に強力なダメージを与える。</t>
+  </si>
+  <si>
+    <t>・기술 사용 중 전방 가드</t>
+  </si>
+  <si>
+    <t>・Forward Guard while using skill</t>
+  </si>
+  <si>
+    <t>・技術使用中の前衛ガード</t>
+  </si>
+  <si>
+    <t>칠흑의 잿더미</t>
+  </si>
+  <si>
+    <t>Pitch-Black Ember</t>
+  </si>
+  <si>
+    <t>漆黒の灰</t>
+  </si>
+  <si>
+    <t>PvE ｜계열 수호 무결한 선명한</t>
+  </si>
+  <si>
+    <t>PvE ｜Branch Aal Aal Serrett</t>
+  </si>
+  <si>
+    <t>PvE ｜系列 守護 無欠한 鮮明한</t>
+  </si>
+  <si>
+    <t>태도에 모인 어둠의 기운을 강력히 휘둘러 방출시킨다.</t>
+  </si>
+  <si>
+    <t>Strongly wields and releases dark energy gathered in the Kriegsmesser.</t>
+  </si>
+  <si>
+    <t>太刀に集められた暗黒エネルギーを強力に操り、放出する。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 5.6초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 5.6 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 5.6秒</t>
+  </si>
+  <si>
+    <t>・Using Skill Super Armor</t>
+  </si>
+  <si>
+    <t>・技術スーパーアーマーの使用方法</t>
+  </si>
+  <si>
+    <t>재앙의 씨앗</t>
+  </si>
+  <si>
+    <t>Seed of Disaster</t>
+  </si>
+  <si>
+    <t>災厄の種</t>
+  </si>
+  <si>
+    <t>憎悪の種</t>
+  </si>
+  <si>
+    <t>적에게 마력의 환영을 소환하여 공격한다.</t>
+  </si>
+  <si>
+    <t>Summons a magical illusion to attack the enemy.</t>
+  </si>
+  <si>
+    <t>魔法の幻想を召喚して敵を攻撃します。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 8.8초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 8.8 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 8.8秒</t>
+  </si>
+  <si>
+    <t>・타격 성공 시 띄우기</t>
+  </si>
+  <si>
+    <t>・Knock-up on successful hit</t>
+  </si>
+  <si>
+    <t>・ヒット成功で浮かせ</t>
+  </si>
+  <si>
+    <t>베디르의 광기</t>
+  </si>
+  <si>
+    <t>Vedir's Madness</t>
+  </si>
+  <si>
+    <t>ベディルの狂気</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜계열 무결 정돈된 희미한</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜Branch Aal Labreve Ahib</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜系列 無欠 洗練された かすかな</t>
+  </si>
+  <si>
+    <t>어두운 기운을 모아 바닥에 태도를 내리 꽃으며 상대를 공격한다.</t>
+  </si>
+  <si>
+    <t>Gather dark energy and slam the Kriegsmesser into the ground to attack the opponent.</t>
+  </si>
+  <si>
+    <t>闇のエネルギーを集めて太刀を地面に叩きつけて相手を攻撃します。</t>
+  </si>
+  <si>
+    <t>황혼의 질주</t>
+  </si>
+  <si>
+    <t>Twilight Sprint</t>
+  </si>
+  <si>
+    <t>黄昏の疾走</t>
+  </si>
+  <si>
+    <t>ファントムチャージ</t>
+  </si>
+  <si>
+    <t>PvP ｜계열 무결 선명한 정돈된</t>
+  </si>
+  <si>
+    <t>PvP ｜系列 無欠 鮮明한 洗練された</t>
+  </si>
+  <si>
+    <t>전방으로 돌진하며 지나간 자리에 피해를 준다.</t>
+  </si>
+  <si>
+    <t>Dashes forward and deals damage in her wake.</t>
+  </si>
+  <si>
+    <t>前方にダッシュし、その後にダメージを与えます。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 6.4초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 6.4 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 6.4秒</t>
+  </si>
+  <si>
+    <t>・최대 11 타격</t>
+  </si>
+  <si>
+    <t>・Max 11 hits</t>
+  </si>
+  <si>
+    <t>・最大11ヒット</t>
+  </si>
+  <si>
+    <t>정령 포식</t>
+  </si>
+  <si>
+    <t>Spirit Devour</t>
+  </si>
+  <si>
+    <t>精霊捕食</t>
+  </si>
+  <si>
+    <t>精霊飽食</t>
+  </si>
+  <si>
+    <t>정령을 불태운 힘을 흡수하여 자신을 치유한다.</t>
+  </si>
+  <si>
+    <t>Absorbs power from burning spirits to heal oneself.</t>
+  </si>
+  <si>
+    <t>燃え盛る精霊の力を吸収して自身を回復する。</t>
+  </si>
+  <si>
+    <t>・10초 간 2초 마다 생명력 회복 115~400</t>
+  </si>
+  <si>
+    <t>・Restores 115~400 HP every 2 seconds for 10 seconds</t>
+  </si>
+  <si>
+    <t>・10秒間、2秒ごとに115〜400の生命力を回復します</t>
+  </si>
+  <si>
+    <t>・30초 간 공격력 +43~100</t>
+  </si>
+  <si>
+    <t>・AP +43~100 for 30 seconds</t>
+  </si>
+  <si>
+    <t>・30秒間AP +43~100</t>
+  </si>
+  <si>
+    <t>・30초 간 방어력 +43~100</t>
+  </si>
+  <si>
+    <t>・DP +43~100 for 30 seconds</t>
+  </si>
+  <si>
+    <t>・30秒間DP+43~100</t>
+  </si>
+  <si>
+    <t>・30초 간 치명타 피해량 +50%</t>
+  </si>
+  <si>
+    <t>・Critical Hit Damage +50% for 30 seconds</t>
+  </si>
+  <si>
+    <t>・30秒間致命打被害量+50%</t>
+  </si>
+  <si>
+    <t>・30초 간 흑정령 기술 피해량 +20%</t>
+  </si>
+  <si>
+    <t>・Black Spirit Skill Damage +20% for 30 seconds</t>
+  </si>
+  <si>
+    <t>・30秒間、闇の精霊技術被害量+20%</t>
+  </si>
+  <si>
+    <t>・기술 사용 시 30초 간 회피 기술 재사용 시간 2초 감소</t>
+  </si>
+  <si>
+    <t>・Evasion Cooldown -2 seconds for 30 seconds upon using skill</t>
+  </si>
+  <si>
+    <t>・技術使用時、30秒間回避再使用待機時間-2秒</t>
+  </si>
+  <si>
+    <t>피어나는 검은 장미</t>
+  </si>
+  <si>
+    <t>Blooming Black Rose</t>
+  </si>
+  <si>
+    <t>咲き誇る黒い薔薇</t>
+  </si>
+  <si>
+    <t>ブルーミングローズ</t>
+  </si>
+  <si>
+    <t>어두운 자연의 기운을 퍼뜨리고, 검은 장미를 피워낸다.</t>
+  </si>
+  <si>
+    <t>Spreads dark nature energy and blooms black roses.</t>
+  </si>
+  <si>
+    <t>闇の自然エネルギーをまき散らし、黒い薔薇を咲かせる。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 16초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 16 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 16秒</t>
+  </si>
+  <si>
+    <t>추락하는 신념</t>
+  </si>
+  <si>
+    <t>Crumbling Faith</t>
+  </si>
+  <si>
+    <t>崩れ落ちる信念</t>
+  </si>
+  <si>
+    <t>墜落する信念</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜계열 무결 선명한 정돈된</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜系列 無欠 鮮明한 洗練された</t>
+  </si>
+  <si>
+    <t>후방으로 도약하며 전방에 환영검을 던져 피해를 입힌다.</t>
+  </si>
+  <si>
+    <t>Leaps backward and throws Phantom Blades forward to deal damage.</t>
+  </si>
+  <si>
+    <t>後方に飛び上がり、ファントムブレードを前方に投げてダメージを与えます。</t>
+  </si>
+  <si>
+    <t>・재사용 대기시간 : 15초</t>
+  </si>
+  <si>
+    <t>・Cooldown: 15 seconds</t>
+  </si>
+  <si>
+    <t>・再使用待機時間: 15秒</t>
+  </si>
+  <si>
+    <t>・기술 사용 중 슈퍼 아머 , 피해 감소 , 잡기 불가</t>
+  </si>
+  <si>
+    <t>・Super Armor , Damage Reduction , Grab Immunity while using skill</t>
+  </si>
+  <si>
+    <t>・スーパーアーマー、被害減少、技術使用時の獲得免疫</t>
+  </si>
+  <si>
+    <t>기울어진 균형</t>
+  </si>
+  <si>
+    <t>Tilted Balance</t>
+  </si>
+  <si>
+    <t>傾いた均衡</t>
+  </si>
+  <si>
+    <t>インバランス</t>
+  </si>
+  <si>
+    <t>대지를 흔들며 어두운 기운을 방출하여 전방의 적에게 강한 충격을 준다.</t>
+  </si>
+  <si>
+    <t>Shakes the earth and releases dark energy to deliver a strong shock to enemies in front.</t>
+  </si>
+  <si>
+    <t>大地を揺るがし暗黒のエネルギーを放出し、前方の敵に強烈な衝撃を与える。</t>
+  </si>
+  <si>
+    <t>어두운 별구름</t>
+  </si>
+  <si>
+    <t>Dark Star Cloud</t>
+  </si>
+  <si>
+    <t>暗い星雲</t>
+  </si>
+  <si>
+    <t>暗然たる雨雲</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜계열 수호 무결 선명한</t>
+  </si>
+  <si>
+    <t>PvE PvP ｜系列 守護 無欠 鮮明한</t>
+  </si>
+  <si>
+    <t>응어리진 어둠의 기운을 터트려 적을 공격한다.</t>
+  </si>
+  <si>
+    <t>Explodes pent-up dark energy to attack enemies.</t>
+  </si>
+  <si>
+    <t>溜まった暗黒エネルギーを爆発させて敵を攻撃します。</t>
+  </si>
+  <si>
+    <t>흑정령의 분노</t>
+  </si>
+  <si>
+    <t>Black Spirit's Rage</t>
+  </si>
+  <si>
+    <t>黒精霊の怒り</t>
+  </si>
+  <si>
+    <t>전방에 흑정령의 기운과 마력을 한 곳에 모아 폭발시킨다.</t>
+  </si>
+  <si>
+    <t>Gathers Black Spirit's energy and Mana in one place in front and detonates it.</t>
+  </si>
+  <si>
+    <t>闇の精霊のエネルギーと魔力を前方一箇所に集めて爆発させる。</t>
+  </si>
+  <si>
+    <t>・기술 사용 중 슈퍼 아머 , 피해 감소</t>
+  </si>
+  <si>
+    <t>・Super Armor , Damage Reduction while using skill</t>
+  </si>
+  <si>
+    <t>・スーパーアーマー、技術使用時の被害減少</t>
+  </si>
+  <si>
+    <t>・무기 선택 : 태도 적용시</t>
+  </si>
+  <si>
+    <t>・When Weapon Selection: Kriegsmesser is applied</t>
+  </si>
+  <si>
+    <t>・武器選択：太刀適用時</t>
+  </si>
+  <si>
+    <t>・최대 6 타격</t>
+  </si>
+  <si>
+    <t>・Max 6 hits</t>
+  </si>
+  <si>
+    <t>・最大6ヒット</t>
+  </si>
+  <si>
+    <t>・무기 선택 : 베디안트 적용시</t>
+  </si>
+  <si>
+    <t>・When Weapon Selection: Vediant is applied</t>
+  </si>
+  <si>
+    <t>・武器選択：ベディアント適用時</t>
+  </si>
+  <si>
+    <t>・최대 5 타격</t>
+  </si>
+  <si>
+    <t>・Max 5 hits</t>
+  </si>
+  <si>
+    <t>・最大5ヒット</t>
+  </si>
+  <si>
+    <t>・타격 성공 시 바운드</t>
+  </si>
+  <si>
+    <t>・Bound on successful hit</t>
+  </si>
+  <si>
+    <t>・ヒット成功時にバインドされる</t>
+  </si>
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>リンデロテ</t>
+  </si>
+  <si>
+    <t>出身地</t>
+  </si>
+  <si>
+    <t>森の外</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>闇のオーラを放ちながら太刀で連続攻撃をする。</t>
+    <rPh sb="0" eb="1">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・打撃成功時、気絶</t>
+    <rPh sb="1" eb="3">
+      <t>ダゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・スキル使用中、スーパーアーマー、キャッチ不可</t>
+    <rPh sb="4" eb="6">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・攻撃中、スーパーアーマー</t>
+    <rPh sb="3" eb="4">
+      <t>ナカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・打撃成功時、気絶</t>
+    <rPh sb="1" eb="3">
+      <t>ダゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・スキル使用地点に、２秒間維持される暗黒の帳幕生成</t>
+    <rPh sb="4" eb="6">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チテン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>アンコク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>マク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・暗黒の帳幕</t>
+    <rPh sb="1" eb="3">
+      <t>アンコク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　0.5秒ごとに魔力12回復</t>
+    <rPh sb="4" eb="5">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　冒険者から受けるダメージ10％減少</t>
+    <rPh sb="1" eb="4">
+      <t>ボウケンシャ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　(効果は自分にのみに適用され、3秒間維持されます)</t>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イジ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1347,13 +1506,7 @@
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="409.55"/>
-      <color rgb="FF000000"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="409.55"/>
+      <sz val="409"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1361,16 +1514,19 @@
     <font>
       <sz val="12"/>
       <color rgb="FF2B2B2B"/>
-      <name val="ＭＳ 明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="409"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF2B2B2B"/>
-      <name val="Roboto"/>
+      <name val="ＭＳ 明朝"/>
       <family val="1"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1399,7 +1555,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1420,7 +1576,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1635,13 +1797,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1656,7 +1818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1673,7 +1835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1687,161 +1849,161 @@
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.5">
       <c r="C10" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.5">
       <c r="C11" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="25.8" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.149999999999999" customHeight="1">
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>376</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="C13" s="5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="13.2" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="8.75" customHeight="1">
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="27.6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28">
       <c r="C15" s="6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>367</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="C16" s="5" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>368</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>369</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1853,13 +2015,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1874,113 +2036,113 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1992,13 +2154,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2013,128 +2175,128 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2146,13 +2308,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2167,113 +2329,113 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2285,13 +2447,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2306,128 +2468,128 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2439,13 +2601,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2460,113 +2622,113 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2578,13 +2740,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2599,143 +2761,143 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2747,13 +2909,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2768,128 +2930,128 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -2901,13 +3063,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2922,128 +3084,128 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3055,13 +3217,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3076,113 +3238,113 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3194,13 +3356,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3215,128 +3377,128 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3348,13 +3510,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3369,218 +3531,218 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="43.2" customHeight="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.75" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="24" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="24" customHeight="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="24" customHeight="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" customHeight="1">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>369</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3592,13 +3754,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3613,113 +3775,113 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3731,13 +3893,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3752,143 +3914,179 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>354</v>
+        <v>376</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="51.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="13" customHeight="1">
+      <c r="A1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="13" customHeight="1">
+      <c r="A2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="13" customHeight="1">
+      <c r="A3" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -3900,13 +4098,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3921,68 +4119,68 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3993,14 +4191,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4015,129 +4213,132 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>115</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>127</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="E10" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -4147,14 +4348,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4169,128 +4370,153 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>146</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>130</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>127</v>
+        <v>149</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="E10" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="E11" s="10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="E12" s="10" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="E13" s="10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="E14" s="10" t="s">
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -4302,13 +4528,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4323,113 +4549,113 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4441,13 +4667,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4462,158 +4688,158 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4625,13 +4851,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4646,143 +4872,143 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4794,13 +5020,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="16" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4815,128 +5041,128 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1">
+    <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
